--- a/tools/importer/reports/import-sample-cards-profile-bio.report.xlsx
+++ b/tools/importer/reports/import-sample-cards-profile-bio.report.xlsx
@@ -79,7 +79,7 @@
     <t>drafts/block-samples/cards-profile-bio</t>
   </si>
   <si>
-    <t>2026-10-01T23:06:32.332Z</t>
+    <t>2026-10-01T23:35:40.509Z</t>
   </si>
   <si>
     <t>Cards Profile Bio — Block Sample</t>
